--- a/config/Excel/system_unlock.xlsx
+++ b/config/Excel/system_unlock.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD314C4D-4165-4A4B-AFFF-A237BA926042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2624F0-BBD7-49A4-AE5C-582A1E3F356D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>系統類型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -100,9 +100,6 @@
     <t>寶石融合</t>
   </si>
   <si>
-    <t>1/3</t>
-  </si>
-  <si>
     <t>等級與轉生次數須同時滿足才開放寶石融合。對應程式 GEM_FUSION_UNLOCK_LEVEL / GEM_FUSION_UNLOCK_REINCARNATIONS。</t>
   </si>
   <si>
@@ -113,6 +110,14 @@
   </si>
   <si>
     <t>等級與轉生次數須同時滿足才開放寶石共鳴；未解鎖前無法查看共鳴頁，滑鼠移到「共鳴」頁籤會以提示顯示解鎖條件。對應程式 GEM_RESONANCE_UNLOCK_LEVEL / GEM_RESONANCE_UNLOCK_REINCARNATION。</t>
+  </si>
+  <si>
+    <t>1/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9999/11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -482,7 +487,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -552,10 +557,10 @@
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -563,13 +568,13 @@
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/system_unlock.xlsx
+++ b/config/Excel/system_unlock.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2624F0-BBD7-49A4-AE5C-582A1E3F356D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F22BCE0-2762-47B2-8223-400B4230B711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_unlock" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <si>
     <t>系統類型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,62 +61,117 @@
     <t>神鑄系統</t>
   </si>
   <si>
+    <t>等級與轉生次數須同時滿足才開放，開放後永久保留，轉生不關閉。對應程式 FORGE_UNLOCK_LEVEL / FORGE_UNLOCK_REINCARNATION。</t>
+  </si>
+  <si>
+    <t>1/0</t>
+  </si>
+  <si>
+    <t>裝備方案 第2套</t>
+  </si>
+  <si>
+    <t>第 2 套裝備方案的解鎖條件（預設開局即開放）。對應程式 EQUIP_SET_UNLOCK_LEVELS[1] / EQUIP_SET_UNLOCK_REINCARNATIONS[1]。</t>
+  </si>
+  <si>
+    <t>裝備方案 第3套</t>
+  </si>
+  <si>
+    <t>第 3 套裝備方案的解鎖條件（預設開局即開放）。對應程式 EQUIP_SET_UNLOCK_LEVELS[2] / EQUIP_SET_UNLOCK_REINCARNATIONS[2]。</t>
+  </si>
+  <si>
+    <t>寶石</t>
+  </si>
+  <si>
+    <t>寶石共鳴</t>
+  </si>
+  <si>
+    <t>1/4</t>
+  </si>
+  <si>
+    <t>等級與轉生次數須同時滿足才開放寶石共鳴；未解鎖前無法查看共鳴頁，滑鼠移到「共鳴」頁籤會以提示顯示解鎖條件。對應程式 GEM_RESONANCE_UNLOCK_LEVEL / GEM_RESONANCE_UNLOCK_REINCARNATION。</t>
+  </si>
+  <si>
+    <t>1/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝備養成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝備神鑄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神鑄四功能之一：裝備神鑄。只看轉生次數（等級欄固定填 1），且須已解鎖神鑄系統。對應程式 DIVINE_FORGE.equipUnlock。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>太古精鑄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神鑄四功能之一：太古精鑄。只看轉生次數（等級欄固定填 1），且須已解鎖神鑄系統。對應程式 DIVINE_FORGE.ancientUnlock。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寶石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神級寶石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神鑄四功能之一：神級寶石。只看轉生次數（等級欄固定填 1），且須已解鎖神鑄系統。對應程式 DIVINE_FORGE.gemUnlock。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神聖刻印</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神鑄四功能之一：神聖刻印。只看轉生次數（等級欄固定填 1），且須已解鎖神鑄系統。對應程式 DIVINE_FORGE.imprintUnlock。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色成長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天堂威能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1/1</t>
-  </si>
-  <si>
-    <t>等級與轉生次數須同時滿足才開放，開放後永久保留，轉生不關閉。對應程式 FORGE_UNLOCK_LEVEL / FORGE_UNLOCK_REINCARNATION。</t>
-  </si>
-  <si>
-    <t>天堂威能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>等級與轉生次數須同時滿足，威能頁籤與威能系統才開放。各威能節點另依 Talents 表的轉數逐轉解鎖（不在本表）。對應程式 TALENT_UNLOCK_LEVEL / TALENT_UNLOCK_REINCARNATION。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>裝備方案 第1套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1/0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>第 1 套裝備方案的解鎖條件（預設開局即開放）。對應程式 EQUIP_SET_UNLOCK_LEVELS[0] / EQUIP_SET_UNLOCK_REINCARNATIONS[0]。</t>
-  </si>
-  <si>
-    <t>裝備方案 第2套</t>
-  </si>
-  <si>
-    <t>第 2 套裝備方案的解鎖條件（預設開局即開放）。對應程式 EQUIP_SET_UNLOCK_LEVELS[1] / EQUIP_SET_UNLOCK_REINCARNATIONS[1]。</t>
-  </si>
-  <si>
-    <t>裝備方案 第3套</t>
-  </si>
-  <si>
-    <t>第 3 套裝備方案的解鎖條件（預設開局即開放）。對應程式 EQUIP_SET_UNLOCK_LEVELS[2] / EQUIP_SET_UNLOCK_REINCARNATIONS[2]。</t>
-  </si>
-  <si>
-    <t>寶石</t>
-  </si>
-  <si>
-    <t>寶石融合</t>
-  </si>
-  <si>
-    <t>等級與轉生次數須同時滿足才開放寶石融合。對應程式 GEM_FUSION_UNLOCK_LEVEL / GEM_FUSION_UNLOCK_REINCARNATIONS。</t>
-  </si>
-  <si>
-    <t>寶石共鳴</t>
-  </si>
-  <si>
-    <t>1/4</t>
-  </si>
-  <si>
-    <t>等級與轉生次數須同時滿足才開放寶石共鳴；未解鎖前無法查看共鳴頁，滑鼠移到「共鳴」頁籤會以提示顯示解鎖條件。對應程式 GEM_RESONANCE_UNLOCK_LEVEL / GEM_RESONANCE_UNLOCK_REINCARNATION。</t>
-  </si>
-  <si>
-    <t>1/2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9999/11</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -443,15 +498,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -465,7 +520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -479,7 +534,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -487,94 +542,136 @@
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/system_unlock.xlsx
+++ b/config/Excel/system_unlock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F22BCE0-2762-47B2-8223-400B4230B711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A11B25-3B1B-4FB8-BBC3-446957A9E937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t>系統類型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -173,6 +173,66 @@
   <si>
     <t>第 1 套裝備方案的解鎖條件（預設開局即開放）。對應程式 EQUIP_SET_UNLOCK_LEVELS[0] / EQUIP_SET_UNLOCK_REINCARNATIONS[0]。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能裝載欄 第3格</t>
+  </si>
+  <si>
+    <t>100/0</t>
+  </si>
+  <si>
+    <t>技能裝載欄第 3 格的解鎖條件（前 2 格開局即有）。等級與轉生次數須同時滿足；只寫等級時，轉生過（≥1 轉）視為已越過。對應程式 LOADOUT_SLOT_UNLOCKS。</t>
+  </si>
+  <si>
+    <t>技能裝載欄 第4格</t>
+  </si>
+  <si>
+    <t>200/0</t>
+  </si>
+  <si>
+    <t>技能裝載欄第 4 格的解鎖條件（前 2 格開局即有）。等級與轉生次數須同時滿足；只寫等級時，轉生過（≥1 轉）視為已越過。對應程式 LOADOUT_SLOT_UNLOCKS。</t>
+  </si>
+  <si>
+    <t>技能裝載欄 第5格</t>
+  </si>
+  <si>
+    <t>300/0</t>
+  </si>
+  <si>
+    <t>技能裝載欄第 5 格的解鎖條件（前 2 格開局即有）。等級與轉生次數須同時滿足；只寫等級時，轉生過（≥1 轉）視為已越過。對應程式 LOADOUT_SLOT_UNLOCKS。</t>
+  </si>
+  <si>
+    <t>技能裝載欄 第6格</t>
+  </si>
+  <si>
+    <t>400/0</t>
+  </si>
+  <si>
+    <t>技能裝載欄第 6 格的解鎖條件（前 2 格開局即有）。等級與轉生次數須同時滿足；只寫等級時，轉生過（≥1 轉）視為已越過。對應程式 LOADOUT_SLOT_UNLOCKS。</t>
+  </si>
+  <si>
+    <t>元素傷害詞條</t>
+  </si>
+  <si>
+    <t>201/0</t>
+  </si>
+  <si>
+    <t>火冰雷毒聖暗地風「屬性傷害提升」八種詞條，裝備等級（掉落、洗煉、詞條池）與角色等級（屬性面板）達此等級才出現。已在裝備上的詞條不受影響。轉生欄只支援 0。例：填 201 ＝ 200 級（含）以前不出現。對應程式 AFFIX_LEVEL_GATES。</t>
+  </si>
+  <si>
+    <t>屬性抗性詞條</t>
+  </si>
+  <si>
+    <t>火冰雷毒聖暗地風八種「屬性抗性」與「全屬性抗性」詞條，規則同「元素傷害詞條」。對應程式 AFFIX_LEVEL_GATES。</t>
+  </si>
+  <si>
+    <t>世界探索</t>
+  </si>
+  <si>
+    <t>神界</t>
+  </si>
+  <si>
+    <t>神界入口（世界地圖的神界傳送門與神界三張地圖）。條件：通關人界最後一張地圖（亡靈山脈 400 關），由 Zones 表的「前置地圖識別碼／前置通關關卡」管理，本列只作索引，改數值請改 Zones 表，這裡的 1/0 不會被程式讀取。</t>
   </si>
 </sst>
 </file>
@@ -498,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -674,6 +734,104 @@
         <v>19</v>
       </c>
     </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
